--- a/content-sheets/museum-of-graffiti-content.xlsx
+++ b/content-sheets/museum-of-graffiti-content.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="428">
   <si>
     <t>template</t>
   </si>
@@ -235,24 +235,156 @@
     <t>product_8_badge</t>
   </si>
   <si>
+    <t>Category Spotlight</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>Category: Collectibles &amp; Toys</t>
+  </si>
+  <si>
+    <t>For the Shelf: One-of-a-Kind Collectibles &amp; Toys</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>#3fbf6f</t>
+  </si>
+  <si>
+    <t>Collectibles &amp; Toys</t>
+  </si>
+  <si>
+    <t>Shop rare toys, limited edition pieces, and artist-designed skate decks inspired by the world of graffiti and street art.</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.com/collections/books-magazines</t>
+  </si>
+  <si>
+    <t>See More &gt;</t>
+  </si>
+  <si>
+    <t>Most Popular</t>
+  </si>
+  <si>
+    <t>THE ICONS</t>
+  </si>
+  <si>
+    <t>ONE OF A KIND</t>
+  </si>
+  <si>
+    <t>Skate With Style</t>
+  </si>
+  <si>
+    <t>Shop Now &gt;</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/FinalDunny1.jpg?v=1736877377</t>
+  </si>
+  <si>
+    <t>20th Anniversary Monochromic Dunny Pin by Tristan Eaton</t>
+  </si>
+  <si>
+    <t>$12.00</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/20th-anniversary-monochromic-dunny-pin-by-tristan-eaton</t>
+  </si>
+  <si>
+    <t>Top Pick</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/KR18704-Andy-Warhol-8-Inch-Masterpiece-Vinyl-Yellow-Brillo-Box-Dunny-Limited-Edition-of-300_01_1000x1000_3a84bc28-d044-4371-b6a3-5057e11a7674.webp?v=1720286587</t>
+  </si>
+  <si>
+    <t>ANDY WARHOL 8" MASTERPIECE VINYL YELLOW BRILLO BOX DUNNY</t>
+  </si>
+  <si>
+    <t>$150.00</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/andy-warhol-8-masterpiece-vinyl-yellow-brillo-box-dunny</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/popeyeskatedeck_dbe6e450-decb-4daa-b682-8c2e8a86fb32.jpg?v=1786740788</t>
+  </si>
+  <si>
+    <t>Slawn and Opake Popeye Skate Deck</t>
+  </si>
+  <si>
+    <t>$100.00</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/slawn-and-opake-popeye-skate-deck</t>
+  </si>
+  <si>
+    <t>Best-Seller</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/Bazaart_AF804A50-B198-46AB-93AD-8E16F205957F_1.jpg?v=1786740846</t>
+  </si>
+  <si>
+    <t>Slawn and Opake Top Cat Skate Deck</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/slawn-and-opake-top-cat-skate-deck</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/RonEnglish_1.jpg?v=1687621347</t>
+  </si>
+  <si>
+    <t>Ron English Frozen Culture Blind Bags</t>
+  </si>
+  <si>
+    <t>$15.00</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/frozen-culture-x-ron-english-mystery-bags</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/SOLO_BEARBRICK51_1024x1024_542b7586-ff65-48e6-9cad-cdaba23ad753.webp?v=1775249555</t>
+  </si>
+  <si>
+    <t>Be@rbrick Series 51 blind box</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/be-rbrick-series-51-blind-box</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/GMP_U2F2ZUdIMDE_b5c89d06-82d7-4c92-b52a-29d465439d48.gif?v=1709487621</t>
+  </si>
+  <si>
+    <t>Crash Canbot - 3 Colorways</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/crash-canbot</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/06E59D7B-AAF5-404C-9BEA-09C17F79F89D.webp?v=1782857254</t>
+  </si>
+  <si>
+    <t>Shuriken by TRAP</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/shuriken-by-trap</t>
+  </si>
+  <si>
     <t>Artist Spotlight</t>
   </si>
   <si>
     <t>2026-08-27</t>
   </si>
   <si>
-    <t>10:00</t>
-  </si>
-  <si>
     <t>Artist Spotlight: Doze Green</t>
   </si>
   <si>
     <t>Meet Doze Green: MOG Exclusive Apparel &amp; Vintage toys</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>#ff8a1f</t>
   </si>
   <si>
@@ -275,12 +407,6 @@
   </si>
   <si>
     <t>https://museumofgraffiti.com/collections/the-gift-shop?filter.p.m.custom.artist=Doze+Green</t>
-  </si>
-  <si>
-    <t>Shop Now &gt;</t>
-  </si>
-  <si>
-    <t>See More &gt;</t>
   </si>
   <si>
     <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/motugdozegreen.jpg?v=1786651895</t>
@@ -437,6 +563,202 @@
     <t>https://museumofgraffiti.myshopify.com/products/skeme-slap-postal-sticker-3-panel-untitled-8</t>
   </si>
   <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>Category: Books &amp; Magazines</t>
+  </si>
+  <si>
+    <t>Required Reading: Graffiti Books &amp; Magazines</t>
+  </si>
+  <si>
+    <t>Books &amp; Magazines</t>
+  </si>
+  <si>
+    <t>Discover the artists, stories, and history behind graffiti culture through our collection of books. From iconic writers to contemporary innovators.</t>
+  </si>
+  <si>
+    <t>Get Inspired</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/1-5717_SX1u0YrkqOwdZyDj_1.jpg?v=1687450849</t>
+  </si>
+  <si>
+    <t>Subway Art</t>
+  </si>
+  <si>
+    <t>$24.95</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/subway-art</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/final2.jpg?v=1691512289</t>
+  </si>
+  <si>
+    <t>BLADE: King of Graffiti</t>
+  </si>
+  <si>
+    <t>$39.99</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/blade-king-of-graffiti</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/graffitialphai-01.webp?v=1784734505</t>
+  </si>
+  <si>
+    <t>Graffiti Alphabets</t>
+  </si>
+  <si>
+    <t>$34.95</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/graffiti-alphabets</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/Graffforbeginners_1680x_d7934d8d-cb00-4bca-9f3d-51d298246401.jpg?v=1687448460</t>
+  </si>
+  <si>
+    <t>Graffiti for Beginners: An Easy Introduction to Drawing Graffiti Letters</t>
+  </si>
+  <si>
+    <t>$11.99</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/graffiti-for-beginners-an-easy-introduction-to-drawing-graffiti-letters</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/Untitled-2_e79de410-46ee-481e-8f87-e26eb3c37c6d.jpg?v=1721079173</t>
+  </si>
+  <si>
+    <t>Miami Graffiti Art Book</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/miami-graffiti-art</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/Untitled-4.png?v=1712003961</t>
+  </si>
+  <si>
+    <t>UP Magazine - Issue #06 Graffiti</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/up-magazine-issue-06-graffiti</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/Graffitistickerbook.jpg?v=1746288420</t>
+  </si>
+  <si>
+    <t>The Graffiti Sticker Book</t>
+  </si>
+  <si>
+    <t>$19.99</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/graffiti-sticker-book</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/fstcrewmag.jpg?v=1703699297</t>
+  </si>
+  <si>
+    <t>FST crew Magazine</t>
+  </si>
+  <si>
+    <t>$35.00</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/fst-crew-magazine</t>
+  </si>
+  <si>
+    <t>Tee of the Month</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>16:27</t>
+  </si>
+  <si>
+    <t>Subscription Tees – August Drop</t>
+  </si>
+  <si>
+    <t>August T-Shirt Drop: YUBIA is Live</t>
+  </si>
+  <si>
+    <t>YUBIA</t>
+  </si>
+  <si>
+    <t>https://d3k81ch9hvuctc.cloudfront.net/company/WHZZ6D/images/ff2456bd-d186-4077-97da-0d13b77fd6c3.jpeg</t>
+  </si>
+  <si>
+    <t>Yubia is a graffiti writer, muralist, and illustrator from Bilbao, Spain, currently based in Barcelona. Active in the graffiti scene since 2002, she has developed a distinctive visual language that blends classic graffiti lettering with playful kawaii-inspired characters, bold color palettes, and contemporary pop culture references. Her work transforms everyday objects, food, spray cans, and urban elements into expressive characters that bring humor, optimism, and energy to walls around the world.</t>
+  </si>
+  <si>
+    <t>We Did It Again. Meet This Month's Shirt Drop.</t>
+  </si>
+  <si>
+    <t>Buy individually or Subscribe &amp; Save 20%</t>
+  </si>
+  <si>
+    <t>$36.00</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.com/collections/2026-writers-tee-drop</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/yubia_front.jpg?v=1785879168</t>
+  </si>
+  <si>
+    <t>August AS COLOUR Drop: Yubia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This exclusive tee is locally hand-screen printed by graffiti artists in our community, keeping the production close to home and helping support the artists and creatives who make our culture what it is.
+This release features artwork by YUBIA, a graffiti writer, muralist, and illustrator from Bilbao…</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/august-drop-presented-by-as-colour-copy</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/Sonic_tee.jpg?v=1784131820</t>
+  </si>
+  <si>
+    <t>July AS COLOUR Drop: Sonic</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/july-drop-presented-by-as-colour</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/Blade_Tee_Front.jpg?v=1782512553</t>
+  </si>
+  <si>
+    <t>June AS COLOUR Drop: Blade</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/june-drop-presented-by-as-colour</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/duel_tee_front.jpg?v=1778684441</t>
+  </si>
+  <si>
+    <t>May AS COLOUR Drop: Duel</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/may-drop-presented-by-as-colour-copy</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/vayne_tee.png?v=1775576683</t>
+  </si>
+  <si>
+    <t>April AS COLOUR Drop: Vayne</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/april-drop-presented-by-as-colour</t>
+  </si>
+  <si>
     <t>2026-08-12</t>
   </si>
   <si>
@@ -495,6 +817,27 @@
   </si>
   <si>
     <t>https://museumofgraffiti.myshopify.com/products/shirt-kings-pioneers-of-hip-hop-fashion</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>Category: Pins, Patches &amp; Stickers</t>
+  </si>
+  <si>
+    <t>Rep the Culture: Pins, Patches &amp; Stickers</t>
+  </si>
+  <si>
+    <t>Stickers &amp; Pins</t>
+  </si>
+  <si>
+    <t>Small in size, big in style. Explore our collection of limited edition stickers and pins inspired by graffiti, street art, and the artists who continue to shape the culture.</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.com/collections/pins-patches-stickers</t>
+  </si>
+  <si>
+    <t>New</t>
   </si>
   <si>
     <t>2026-08-09</t>
@@ -537,9 +880,6 @@
     <t>ABSTRK Hand Embellished Print 2026</t>
   </si>
   <si>
-    <t>$150.00</t>
-  </si>
-  <si>
     <t>https://museumofgraffiti.myshopify.com/products/abstrk-hand-embellished-print-2026</t>
   </si>
   <si>
@@ -573,6 +913,25 @@
     <t>https://museumofgraffiti.myshopify.com/products/abstrk-x-levis-denim-shorts-size-34</t>
   </si>
   <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>10:12</t>
+  </si>
+  <si>
+    <t>Subscription Tees – Evergreen</t>
+  </si>
+  <si>
+    <t>12 Writers. 12 Months. One Membership.</t>
+  </si>
+  <si>
+    <t>Artist Tee Membership · Presented by AS Colour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every month, a legendary graffiti writer drops one exclusive, limited-edition tee — printed on premium AS Colour blanks and delivered right to your door.
+ Buy them individually or Subscribe and Save 20%</t>
+  </si>
+  <si>
     <t>2026-08-05</t>
   </si>
   <si>
@@ -580,9 +939,6 @@
   </si>
   <si>
     <t>Meet COCO144: New Limited-Edition Releases Are Here</t>
-  </si>
-  <si>
-    <t>#3fbf6f</t>
   </si>
   <si>
     <t>COCO144</t>
@@ -657,159 +1013,6 @@
     <t>https://museumofgraffiti.myshopify.com/products/coco144-limited-edition-prints-green</t>
   </si>
   <si>
-    <t>Category Spotlight</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>Category: Books &amp; Magazines</t>
-  </si>
-  <si>
-    <t>Required Reading: Graffiti Books &amp; Magazines</t>
-  </si>
-  <si>
-    <t>Books &amp; Magazines</t>
-  </si>
-  <si>
-    <t>Discover the artists, stories, and history behind graffiti culture through our collection of books. From iconic writers to contemporary innovators.</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.com/collections/books-magazines</t>
-  </si>
-  <si>
-    <t>Most Popular</t>
-  </si>
-  <si>
-    <t>THE ICONS</t>
-  </si>
-  <si>
-    <t>ONE OF A KIND</t>
-  </si>
-  <si>
-    <t>Get Inspired</t>
-  </si>
-  <si>
-    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/1-5717_SX1u0YrkqOwdZyDj_1.jpg?v=1687450849</t>
-  </si>
-  <si>
-    <t>Subway Art</t>
-  </si>
-  <si>
-    <t>$24.95</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.myshopify.com/products/subway-art</t>
-  </si>
-  <si>
-    <t>Best-Seller</t>
-  </si>
-  <si>
-    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/final2.jpg?v=1691512289</t>
-  </si>
-  <si>
-    <t>BLADE: King of Graffiti</t>
-  </si>
-  <si>
-    <t>$39.99</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.myshopify.com/products/blade-king-of-graffiti</t>
-  </si>
-  <si>
-    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/graffitialphai-01.webp?v=1784734505</t>
-  </si>
-  <si>
-    <t>Graffiti Alphabets</t>
-  </si>
-  <si>
-    <t>$34.95</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.myshopify.com/products/graffiti-alphabets</t>
-  </si>
-  <si>
-    <t>Top Pick</t>
-  </si>
-  <si>
-    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/Graffforbeginners_1680x_d7934d8d-cb00-4bca-9f3d-51d298246401.jpg?v=1687448460</t>
-  </si>
-  <si>
-    <t>Graffiti for Beginners: An Easy Introduction to Drawing Graffiti Letters</t>
-  </si>
-  <si>
-    <t>$11.99</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.myshopify.com/products/graffiti-for-beginners-an-easy-introduction-to-drawing-graffiti-letters</t>
-  </si>
-  <si>
-    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/Untitled-2_e79de410-46ee-481e-8f87-e26eb3c37c6d.jpg?v=1721079173</t>
-  </si>
-  <si>
-    <t>Miami Graffiti Art Book</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.myshopify.com/products/miami-graffiti-art</t>
-  </si>
-  <si>
-    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/Untitled-4.png?v=1712003961</t>
-  </si>
-  <si>
-    <t>UP Magazine - Issue #06 Graffiti</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.myshopify.com/products/up-magazine-issue-06-graffiti</t>
-  </si>
-  <si>
-    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/Graffitistickerbook.jpg?v=1746288420</t>
-  </si>
-  <si>
-    <t>The Graffiti Sticker Book</t>
-  </si>
-  <si>
-    <t>$19.99</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.myshopify.com/products/graffiti-sticker-book</t>
-  </si>
-  <si>
-    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/fstcrewmag.jpg?v=1703699297</t>
-  </si>
-  <si>
-    <t>FST crew Magazine</t>
-  </si>
-  <si>
-    <t>$35.00</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.myshopify.com/products/fst-crew-magazine</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>Category: Pins, Patches &amp; Stickers</t>
-  </si>
-  <si>
-    <t>Rep the Culture: Pins, Patches &amp; Stickers</t>
-  </si>
-  <si>
-    <t>Stickers &amp; Pins</t>
-  </si>
-  <si>
-    <t>Small in size, big in style. Explore our collection of limited edition stickers and pins inspired by graffiti, street art, and the artists who continue to shape the culture.</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.com/collections/pins-patches-stickers</t>
-  </si>
-  <si>
-    <t>New</t>
-  </si>
-  <si>
     <t>2026-08-03</t>
   </si>
   <si>
@@ -888,6 +1091,39 @@
     <t>https://museumofgraffiti.myshopify.com/products/crook-and-crome-poster</t>
   </si>
   <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>14:48</t>
+  </si>
+  <si>
+    <t>Subscription Tees – July Drop</t>
+  </si>
+  <si>
+    <t>Exclusive T-Shirt Drop: SONIC Is Live</t>
+  </si>
+  <si>
+    <t>SONIC</t>
+  </si>
+  <si>
+    <t>https://d3k81ch9hvuctc.cloudfront.net/company/WHZZ6D/images/5fa0dd86-e736-4d7f-9020-07a05afc7645.jpeg</t>
+  </si>
+  <si>
+    <t>Jesse Rodriguez, born and raised in New York City, found his artistic calling in graffiti during the early 1970s. Sonic pioneered unique graffiti styles, introducing 3D folding letters and transforming letters into characters, leaving an indelible mark on Hip Hop culture. Painting NYC subway trains posed numerous challenges for Sonic: from stealing spray paint to navigating the city’s dangers en route to train yards, the process involved sneaking in and facing constant police pursuits. Despite these obstacles, Sonic’s determination and passion for his craft drove him to leave a lasting imprint on the subway cars, contributing to the vibrant and rebellious culture of graffiti in the 1970s and beyond. Notable works like “Revolution 81” and “World War III” on NYC subway cars showcase his influence.</t>
+  </si>
+  <si>
+    <t>This exclusive shirt features artwork by SONIC (also known as Sonic Bad or Jesse Rodriguez), one of New York City's most influential graffiti pioneers. Renowned for developing the groundbreaking 3D "folding" and "ribbon letter" style, SONIC helped redefine the visual language of graffiti during the …</t>
+  </si>
+  <si>
+    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/tesoe.jpg?v=1772466076</t>
+  </si>
+  <si>
+    <t>March AS COLOUR Drop: Tesoe</t>
+  </si>
+  <si>
+    <t>https://museumofgraffiti.myshopify.com/products/march-drop-presented-by-as-colour</t>
+  </si>
+  <si>
     <t>2026-07-24</t>
   </si>
   <si>
@@ -1068,195 +1304,7 @@
     <t>Bobby Ellis Traditional Tattoo Ceramic Mug</t>
   </si>
   <si>
-    <t>$15.00</t>
-  </si>
-  <si>
     <t>https://museumofgraffiti.myshopify.com/products/bobby-ellis-traditional-tattoo-ceramic-mugs</t>
-  </si>
-  <si>
-    <t>2026-07-14</t>
-  </si>
-  <si>
-    <t>Category: Apparel</t>
-  </si>
-  <si>
-    <t>Apparel</t>
-  </si>
-  <si>
-    <t>Wear the movement - artist tees, crewnecks, hoodies, and hats from the writers we show and the house we built.</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.com/collections/apparel</t>
-  </si>
-  <si>
-    <t>Top New Drops</t>
-  </si>
-  <si>
-    <t>HOUSE STAPLES</t>
-  </si>
-  <si>
-    <t>June T-Shirt Drop</t>
-  </si>
-  <si>
-    <t>2026-07-10</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>Fresh Ink: New Prints &amp; Posters</t>
-  </si>
-  <si>
-    <t>#22c3d6</t>
-  </si>
-  <si>
-    <t>Prints &amp; Posters</t>
-  </si>
-  <si>
-    <t>Sign your walls - exhibition posters, signed editions, and hand-embellished originals from the artists we show.</t>
-  </si>
-  <si>
-    <t>Fan Favorites</t>
-  </si>
-  <si>
-    <t>TOP PICKS</t>
-  </si>
-  <si>
-    <t>Tee of the Month</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>16:27</t>
-  </si>
-  <si>
-    <t>Subscription Tees – August Drop</t>
-  </si>
-  <si>
-    <t>August T-Shirt Drop: YUBIA is Live</t>
-  </si>
-  <si>
-    <t>YUBIA</t>
-  </si>
-  <si>
-    <t>https://d3k81ch9hvuctc.cloudfront.net/company/WHZZ6D/images/ff2456bd-d186-4077-97da-0d13b77fd6c3.jpeg</t>
-  </si>
-  <si>
-    <t>Yubia is a graffiti writer, muralist, and illustrator from Bilbao, Spain, currently based in Barcelona. Active in the graffiti scene since 2002, she has developed a distinctive visual language that blends classic graffiti lettering with playful kawaii-inspired characters, bold color palettes, and contemporary pop culture references. Her work transforms everyday objects, food, spray cans, and urban elements into expressive characters that bring humor, optimism, and energy to walls around the world.</t>
-  </si>
-  <si>
-    <t>We Did It Again. Meet This Month's Shirt Drop.</t>
-  </si>
-  <si>
-    <t>Buy individually or Subscribe &amp; Save 20%</t>
-  </si>
-  <si>
-    <t>$36.00</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.com/collections/2026-writers-tee-drop</t>
-  </si>
-  <si>
-    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/yubia_front.jpg?v=1785879168</t>
-  </si>
-  <si>
-    <t>August AS COLOUR Drop: Yubia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This exclusive tee is locally hand-screen printed by graffiti artists in our community, keeping the production close to home and helping support the artists and creatives who make our culture what it is.
-This release features artwork by YUBIA, a graffiti writer, muralist, and illustrator from Bilbao…</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.myshopify.com/products/august-drop-presented-by-as-colour-copy</t>
-  </si>
-  <si>
-    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/Sonic_tee.jpg?v=1784131820</t>
-  </si>
-  <si>
-    <t>July AS COLOUR Drop: Sonic</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.myshopify.com/products/july-drop-presented-by-as-colour</t>
-  </si>
-  <si>
-    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/Blade_Tee_Front.jpg?v=1782512553</t>
-  </si>
-  <si>
-    <t>June AS COLOUR Drop: Blade</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.myshopify.com/products/june-drop-presented-by-as-colour</t>
-  </si>
-  <si>
-    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/duel_tee_front.jpg?v=1778684441</t>
-  </si>
-  <si>
-    <t>May AS COLOUR Drop: Duel</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.myshopify.com/products/may-drop-presented-by-as-colour-copy</t>
-  </si>
-  <si>
-    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/vayne_tee.png?v=1775576683</t>
-  </si>
-  <si>
-    <t>April AS COLOUR Drop: Vayne</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.myshopify.com/products/april-drop-presented-by-as-colour</t>
-  </si>
-  <si>
-    <t>2026-08-07</t>
-  </si>
-  <si>
-    <t>10:12</t>
-  </si>
-  <si>
-    <t>Subscription Tees – Evergreen</t>
-  </si>
-  <si>
-    <t>12 Writers. 12 Months. One Membership.</t>
-  </si>
-  <si>
-    <t>Artist Tee Membership · Presented by AS Colour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every month, a legendary graffiti writer drops one exclusive, limited-edition tee — printed on premium AS Colour blanks and delivered right to your door.
- Buy them individually or Subscribe and Save 20%</t>
-  </si>
-  <si>
-    <t>2026-08-01</t>
-  </si>
-  <si>
-    <t>14:48</t>
-  </si>
-  <si>
-    <t>Subscription Tees – July Drop</t>
-  </si>
-  <si>
-    <t>Exclusive T-Shirt Drop: SONIC Is Live</t>
-  </si>
-  <si>
-    <t>SONIC</t>
-  </si>
-  <si>
-    <t>https://d3k81ch9hvuctc.cloudfront.net/company/WHZZ6D/images/5fa0dd86-e736-4d7f-9020-07a05afc7645.jpeg</t>
-  </si>
-  <si>
-    <t>Jesse Rodriguez, born and raised in New York City, found his artistic calling in graffiti during the early 1970s. Sonic pioneered unique graffiti styles, introducing 3D folding letters and transforming letters into characters, leaving an indelible mark on Hip Hop culture. Painting NYC subway trains posed numerous challenges for Sonic: from stealing spray paint to navigating the city’s dangers en route to train yards, the process involved sneaking in and facing constant police pursuits. Despite these obstacles, Sonic’s determination and passion for his craft drove him to leave a lasting imprint on the subway cars, contributing to the vibrant and rebellious culture of graffiti in the 1970s and beyond. Notable works like “Revolution 81” and “World War III” on NYC subway cars showcase his influence.</t>
-  </si>
-  <si>
-    <t>This exclusive shirt features artwork by SONIC (also known as Sonic Bad or Jesse Rodriguez), one of New York City's most influential graffiti pioneers. Renowned for developing the groundbreaking 3D "folding" and "ribbon letter" style, SONIC helped redefine the visual language of graffiti during the …</t>
-  </si>
-  <si>
-    <t>https://cdn.shopify.com/s/files/1/0630/0444/2851/files/tesoe.jpg?v=1772466076</t>
-  </si>
-  <si>
-    <t>March AS COLOUR Drop: Tesoe</t>
-  </si>
-  <si>
-    <t>https://museumofgraffiti.myshopify.com/products/march-drop-presented-by-as-colour</t>
   </si>
 </sst>
 </file>
@@ -1637,7 +1685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BV16"/>
+  <dimension ref="A1:BV15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="11" width="14" customWidth="1"/>
@@ -1924,79 +1972,79 @@
         <v>80</v>
       </c>
       <c r="I2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="N2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="O2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="P2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="Q2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="R2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="S2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="T2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="U2" t="s">
+        <v>79</v>
+      </c>
+      <c r="V2" t="s">
+        <v>79</v>
+      </c>
+      <c r="W2" t="s">
+        <v>79</v>
+      </c>
+      <c r="X2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF2" t="s">
         <v>83</v>
       </c>
-      <c r="V2" t="s">
+      <c r="AG2" t="s">
         <v>84</v>
-      </c>
-      <c r="W2" t="s">
-        <v>85</v>
-      </c>
-      <c r="X2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>89</v>
       </c>
       <c r="AH2" t="s">
         <v>90</v>
@@ -2005,118 +2053,118 @@
         <v>91</v>
       </c>
       <c r="AJ2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK2" t="s">
         <v>92</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
         <v>93</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" t="s">
         <v>94</v>
       </c>
-      <c r="AM2" t="s">
-        <v>79</v>
-      </c>
       <c r="AN2" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="AO2" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="AP2" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="AQ2" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="AR2" t="s">
         <v>79</v>
       </c>
       <c r="AS2" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AT2" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AU2" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AV2" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AW2" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AX2" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="AY2" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="AZ2" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="BA2" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="BB2" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="BC2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="BD2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="BE2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>110</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>114</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>101</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>116</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>79</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT2" t="s">
         <v>97</v>
       </c>
-      <c r="BF2" t="s">
-        <v>98</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>99</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>100</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>101</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>102</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>103</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>104</v>
-      </c>
-      <c r="BO2" t="s">
-        <v>105</v>
-      </c>
-      <c r="BP2" t="s">
-        <v>106</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>79</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>107</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>108</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>109</v>
-      </c>
       <c r="BU2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="BV2" t="s">
         <v>79</v>
@@ -2124,28 +2172,28 @@
     </row>
     <row r="3" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="F3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="G3" t="s">
         <v>79</v>
       </c>
       <c r="H3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="I3" t="s">
         <v>79</v>
@@ -2178,25 +2226,25 @@
         <v>79</v>
       </c>
       <c r="S3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="T3" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="U3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="V3" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="W3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="X3" t="s">
         <v>79</v>
       </c>
       <c r="Y3" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="Z3" t="s">
         <v>79</v>
@@ -2211,31 +2259,31 @@
         <v>79</v>
       </c>
       <c r="AD3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="AE3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF3" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="AG3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AH3" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="AI3" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="AJ3" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="AK3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="AL3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="AM3" t="s">
         <v>79</v>
@@ -2286,61 +2334,61 @@
         <v>79</v>
       </c>
       <c r="BC3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="BD3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="BE3" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="BF3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BG3" t="s">
         <v>79</v>
       </c>
       <c r="BH3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="BI3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="BJ3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="BK3" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="BL3" t="s">
         <v>79</v>
       </c>
       <c r="BM3" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="BN3" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="BO3" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="BP3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="BQ3" t="s">
         <v>79</v>
       </c>
       <c r="BR3" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="BS3" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="BT3" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="BU3" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="BV3" t="s">
         <v>79</v>
@@ -2348,28 +2396,28 @@
     </row>
     <row r="4" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="F4" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="G4" t="s">
         <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="I4" t="s">
         <v>79</v>
@@ -2402,25 +2450,25 @@
         <v>79</v>
       </c>
       <c r="S4" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="T4" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="U4" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="V4" t="s">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="W4" t="s">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="X4" t="s">
         <v>79</v>
       </c>
       <c r="Y4" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="Z4" t="s">
         <v>79</v>
@@ -2435,31 +2483,31 @@
         <v>79</v>
       </c>
       <c r="AD4" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="AE4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF4" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="AG4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AH4" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="AI4" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="AJ4" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="AK4" t="s">
-        <v>105</v>
+        <v>167</v>
       </c>
       <c r="AL4" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="AM4" t="s">
         <v>79</v>
@@ -2510,61 +2558,61 @@
         <v>79</v>
       </c>
       <c r="BC4" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="BD4" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="BE4" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="BF4" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="BG4" t="s">
         <v>79</v>
       </c>
       <c r="BH4" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="BI4" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="BJ4" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="BK4" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="BL4" t="s">
         <v>79</v>
       </c>
       <c r="BM4" t="s">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="BN4" t="s">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="BO4" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="BP4" t="s">
-        <v>79</v>
+        <v>178</v>
       </c>
       <c r="BQ4" t="s">
         <v>79</v>
       </c>
       <c r="BR4" t="s">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="BS4" t="s">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="BT4" t="s">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="BU4" t="s">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="BV4" t="s">
         <v>79</v>
@@ -2575,64 +2623,64 @@
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C5" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="E5" t="s">
         <v>74</v>
       </c>
       <c r="F5" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="G5" t="s">
         <v>79</v>
       </c>
       <c r="H5" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="I5" t="s">
-        <v>79</v>
+        <v>186</v>
       </c>
       <c r="J5" t="s">
-        <v>79</v>
+        <v>187</v>
       </c>
       <c r="K5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L5" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="N5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="O5" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="P5" t="s">
-        <v>79</v>
+        <v>188</v>
       </c>
       <c r="Q5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="R5" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="S5" t="s">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="T5" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="U5" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
@@ -2644,7 +2692,7 @@
         <v>79</v>
       </c>
       <c r="Y5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="Z5" t="s">
         <v>79</v>
@@ -2659,136 +2707,136 @@
         <v>79</v>
       </c>
       <c r="AD5" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="AE5" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AF5" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AG5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AH5" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="AI5" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="AJ5" t="s">
-        <v>169</v>
+        <v>79</v>
       </c>
       <c r="AK5" t="s">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="AL5" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="AM5" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AN5" t="s">
-        <v>79</v>
+        <v>193</v>
       </c>
       <c r="AO5" t="s">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="AP5" t="s">
-        <v>79</v>
+        <v>195</v>
       </c>
       <c r="AQ5" t="s">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="AR5" t="s">
         <v>79</v>
       </c>
       <c r="AS5" t="s">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="AT5" t="s">
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="AU5" t="s">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AV5" t="s">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="AW5" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="AX5" t="s">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="AY5" t="s">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="AZ5" t="s">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="BA5" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="BB5" t="s">
         <v>79</v>
       </c>
       <c r="BC5" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="BD5" t="s">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="BE5" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="BF5" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="BG5" t="s">
         <v>79</v>
       </c>
       <c r="BH5" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="BI5" t="s">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="BJ5" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="BK5" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="BL5" t="s">
         <v>79</v>
       </c>
       <c r="BM5" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="BN5" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="BO5" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="BP5" t="s">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="BQ5" t="s">
         <v>79</v>
       </c>
       <c r="BR5" t="s">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="BS5" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="BT5" t="s">
-        <v>177</v>
+        <v>217</v>
       </c>
       <c r="BU5" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="BV5" t="s">
         <v>79</v>
@@ -2796,28 +2844,28 @@
     </row>
     <row r="6" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>219</v>
       </c>
       <c r="B6" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>221</v>
       </c>
       <c r="D6" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>219</v>
       </c>
       <c r="F6" t="s">
-        <v>187</v>
+        <v>223</v>
       </c>
       <c r="G6" t="s">
         <v>79</v>
       </c>
       <c r="H6" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="I6" t="s">
         <v>79</v>
@@ -2850,64 +2898,64 @@
         <v>79</v>
       </c>
       <c r="S6" t="s">
-        <v>189</v>
+        <v>224</v>
       </c>
       <c r="T6" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="U6" t="s">
-        <v>191</v>
+        <v>79</v>
       </c>
       <c r="V6" t="s">
-        <v>192</v>
+        <v>79</v>
       </c>
       <c r="W6" t="s">
         <v>79</v>
       </c>
       <c r="X6" t="s">
-        <v>79</v>
+        <v>226</v>
       </c>
       <c r="Y6" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="Z6" t="s">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="AA6" t="s">
-        <v>79</v>
+        <v>228</v>
       </c>
       <c r="AB6" t="s">
-        <v>79</v>
+        <v>229</v>
       </c>
       <c r="AC6" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="AD6" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="AE6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AF6" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="AG6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AH6" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="AI6" t="s">
-        <v>195</v>
+        <v>232</v>
       </c>
       <c r="AJ6" t="s">
-        <v>196</v>
+        <v>233</v>
       </c>
       <c r="AK6" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="AL6" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="AM6" t="s">
         <v>79</v>
@@ -2958,61 +3006,61 @@
         <v>79</v>
       </c>
       <c r="BC6" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="BD6" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="BE6" t="s">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="BF6" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="BG6" t="s">
         <v>79</v>
       </c>
       <c r="BH6" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="BI6" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="BJ6" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="BK6" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="BL6" t="s">
         <v>79</v>
       </c>
       <c r="BM6" t="s">
-        <v>206</v>
+        <v>241</v>
       </c>
       <c r="BN6" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="BO6" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="BP6" t="s">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="BQ6" t="s">
         <v>79</v>
       </c>
       <c r="BR6" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="BS6" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="BT6" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="BU6" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="BV6" t="s">
         <v>79</v>
@@ -3020,223 +3068,223 @@
     </row>
     <row r="7" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>212</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="C7" t="s">
-        <v>214</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>215</v>
+        <v>248</v>
       </c>
       <c r="E7" t="s">
-        <v>212</v>
+        <v>120</v>
       </c>
       <c r="F7" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="G7" t="s">
         <v>79</v>
       </c>
       <c r="H7" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="I7" t="s">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s">
-        <v>218</v>
+        <v>79</v>
       </c>
       <c r="K7" t="s">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="L7" t="s">
+        <v>79</v>
+      </c>
+      <c r="M7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O7" t="s">
+        <v>79</v>
+      </c>
+      <c r="P7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>79</v>
+      </c>
+      <c r="R7" t="s">
+        <v>79</v>
+      </c>
+      <c r="S7" t="s">
+        <v>250</v>
+      </c>
+      <c r="T7" t="s">
+        <v>251</v>
+      </c>
+      <c r="U7" t="s">
+        <v>252</v>
+      </c>
+      <c r="V7" t="s">
+        <v>79</v>
+      </c>
+      <c r="W7" t="s">
+        <v>79</v>
+      </c>
+      <c r="X7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE7" t="s">
         <v>89</v>
       </c>
-      <c r="M7" t="s">
-        <v>220</v>
-      </c>
-      <c r="N7" t="s">
-        <v>221</v>
-      </c>
-      <c r="O7" t="s">
-        <v>222</v>
-      </c>
-      <c r="P7" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>219</v>
-      </c>
-      <c r="R7" t="s">
-        <v>88</v>
-      </c>
-      <c r="S7" t="s">
-        <v>79</v>
-      </c>
-      <c r="T7" t="s">
-        <v>79</v>
-      </c>
-      <c r="U7" t="s">
-        <v>79</v>
-      </c>
-      <c r="V7" t="s">
-        <v>79</v>
-      </c>
-      <c r="W7" t="s">
-        <v>79</v>
-      </c>
-      <c r="X7" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>79</v>
-      </c>
       <c r="AF7" t="s">
-        <v>219</v>
+        <v>254</v>
       </c>
       <c r="AG7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AH7" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="AI7" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="AJ7" t="s">
-        <v>79</v>
+        <v>257</v>
       </c>
       <c r="AK7" t="s">
-        <v>226</v>
+        <v>147</v>
       </c>
       <c r="AL7" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="AM7" t="s">
-        <v>228</v>
+        <v>79</v>
       </c>
       <c r="AN7" t="s">
-        <v>229</v>
+        <v>79</v>
       </c>
       <c r="AO7" t="s">
-        <v>230</v>
+        <v>79</v>
       </c>
       <c r="AP7" t="s">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="AQ7" t="s">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="AR7" t="s">
         <v>79</v>
       </c>
       <c r="AS7" t="s">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="AT7" t="s">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="AU7" t="s">
-        <v>235</v>
+        <v>79</v>
       </c>
       <c r="AV7" t="s">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="AW7" t="s">
-        <v>237</v>
+        <v>79</v>
       </c>
       <c r="AX7" t="s">
-        <v>238</v>
+        <v>79</v>
       </c>
       <c r="AY7" t="s">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="AZ7" t="s">
-        <v>240</v>
+        <v>79</v>
       </c>
       <c r="BA7" t="s">
-        <v>241</v>
+        <v>79</v>
       </c>
       <c r="BB7" t="s">
         <v>79</v>
       </c>
       <c r="BC7" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="BD7" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="BE7" t="s">
-        <v>101</v>
+        <v>261</v>
       </c>
       <c r="BF7" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="BG7" t="s">
         <v>79</v>
       </c>
       <c r="BH7" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="BI7" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="BJ7" t="s">
-        <v>109</v>
+        <v>265</v>
       </c>
       <c r="BK7" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="BL7" t="s">
         <v>79</v>
       </c>
       <c r="BM7" t="s">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="BN7" t="s">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="BO7" t="s">
-        <v>250</v>
+        <v>79</v>
       </c>
       <c r="BP7" t="s">
-        <v>251</v>
+        <v>79</v>
       </c>
       <c r="BQ7" t="s">
         <v>79</v>
       </c>
       <c r="BR7" t="s">
-        <v>252</v>
+        <v>79</v>
       </c>
       <c r="BS7" t="s">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="BT7" t="s">
-        <v>254</v>
+        <v>79</v>
       </c>
       <c r="BU7" t="s">
-        <v>255</v>
+        <v>79</v>
       </c>
       <c r="BV7" t="s">
         <v>79</v>
@@ -3244,59 +3292,59 @@
     </row>
     <row r="8" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>212</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C8" t="s">
         <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="E8" t="s">
-        <v>212</v>
+        <v>74</v>
       </c>
       <c r="F8" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="G8" t="s">
         <v>79</v>
       </c>
       <c r="H8" t="s">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="I8" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="J8" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="K8" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="L8" t="s">
+        <v>84</v>
+      </c>
+      <c r="M8" t="s">
+        <v>85</v>
+      </c>
+      <c r="N8" t="s">
+        <v>86</v>
+      </c>
+      <c r="O8" t="s">
+        <v>87</v>
+      </c>
+      <c r="P8" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>272</v>
+      </c>
+      <c r="R8" t="s">
         <v>89</v>
       </c>
-      <c r="M8" t="s">
-        <v>220</v>
-      </c>
-      <c r="N8" t="s">
-        <v>221</v>
-      </c>
-      <c r="O8" t="s">
-        <v>222</v>
-      </c>
-      <c r="P8" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>261</v>
-      </c>
-      <c r="R8" t="s">
-        <v>88</v>
-      </c>
       <c r="S8" t="s">
         <v>79</v>
       </c>
@@ -3337,10 +3385,10 @@
         <v>79</v>
       </c>
       <c r="AF8" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="AG8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AH8" t="s">
         <v>79</v>
@@ -3358,7 +3406,7 @@
         <v>79</v>
       </c>
       <c r="AM8" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="AN8" t="s">
         <v>79</v>
@@ -3373,7 +3421,7 @@
         <v>79</v>
       </c>
       <c r="AR8" t="s">
-        <v>228</v>
+        <v>103</v>
       </c>
       <c r="AS8" t="s">
         <v>79</v>
@@ -3468,223 +3516,223 @@
     </row>
     <row r="9" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>212</v>
+        <v>120</v>
       </c>
       <c r="B9" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>275</v>
       </c>
       <c r="D9" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="E9" t="s">
-        <v>212</v>
+        <v>120</v>
       </c>
       <c r="F9" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="G9" t="s">
         <v>79</v>
       </c>
       <c r="H9" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="I9" t="s">
-        <v>266</v>
+        <v>79</v>
       </c>
       <c r="J9" t="s">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="K9" t="s">
-        <v>268</v>
+        <v>79</v>
       </c>
       <c r="L9" t="s">
+        <v>79</v>
+      </c>
+      <c r="M9" t="s">
+        <v>79</v>
+      </c>
+      <c r="N9" t="s">
+        <v>79</v>
+      </c>
+      <c r="O9" t="s">
+        <v>79</v>
+      </c>
+      <c r="P9" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>79</v>
+      </c>
+      <c r="R9" t="s">
+        <v>79</v>
+      </c>
+      <c r="S9" t="s">
+        <v>278</v>
+      </c>
+      <c r="T9" t="s">
+        <v>279</v>
+      </c>
+      <c r="U9" t="s">
+        <v>280</v>
+      </c>
+      <c r="V9" t="s">
+        <v>79</v>
+      </c>
+      <c r="W9" t="s">
+        <v>79</v>
+      </c>
+      <c r="X9" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>163</v>
+      </c>
+      <c r="AE9" t="s">
         <v>89</v>
       </c>
-      <c r="M9" t="s">
-        <v>220</v>
-      </c>
-      <c r="N9" t="s">
-        <v>221</v>
-      </c>
-      <c r="O9" t="s">
-        <v>222</v>
-      </c>
-      <c r="P9" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>268</v>
-      </c>
-      <c r="R9" t="s">
-        <v>88</v>
-      </c>
-      <c r="S9" t="s">
-        <v>79</v>
-      </c>
-      <c r="T9" t="s">
-        <v>79</v>
-      </c>
-      <c r="U9" t="s">
-        <v>79</v>
-      </c>
-      <c r="V9" t="s">
-        <v>79</v>
-      </c>
-      <c r="W9" t="s">
-        <v>79</v>
-      </c>
-      <c r="X9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>79</v>
-      </c>
       <c r="AF9" t="s">
-        <v>268</v>
+        <v>163</v>
       </c>
       <c r="AG9" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AH9" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AI9" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="AJ9" t="s">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="AK9" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="AL9" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="AM9" t="s">
-        <v>228</v>
+        <v>79</v>
       </c>
       <c r="AN9" t="s">
-        <v>272</v>
+        <v>79</v>
       </c>
       <c r="AO9" t="s">
-        <v>273</v>
+        <v>79</v>
       </c>
       <c r="AP9" t="s">
-        <v>274</v>
+        <v>79</v>
       </c>
       <c r="AQ9" t="s">
-        <v>275</v>
+        <v>79</v>
       </c>
       <c r="AR9" t="s">
-        <v>237</v>
+        <v>79</v>
       </c>
       <c r="AS9" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="AT9" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="AU9" t="s">
         <v>79</v>
       </c>
       <c r="AV9" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="AW9" t="s">
         <v>79</v>
       </c>
       <c r="AX9" t="s">
-        <v>276</v>
+        <v>79</v>
       </c>
       <c r="AY9" t="s">
-        <v>277</v>
+        <v>79</v>
       </c>
       <c r="AZ9" t="s">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="BA9" t="s">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="BB9" t="s">
         <v>79</v>
       </c>
       <c r="BC9" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="BD9" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="BE9" t="s">
-        <v>274</v>
+        <v>97</v>
       </c>
       <c r="BF9" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="BG9" t="s">
         <v>79</v>
       </c>
       <c r="BH9" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="BI9" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="BJ9" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="BK9" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="BL9" t="s">
         <v>79</v>
       </c>
       <c r="BM9" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="BN9" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="BO9" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="BP9" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="BQ9" t="s">
         <v>79</v>
       </c>
       <c r="BR9" t="s">
-        <v>79</v>
+        <v>295</v>
       </c>
       <c r="BS9" t="s">
-        <v>79</v>
+        <v>296</v>
       </c>
       <c r="BT9" t="s">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="BU9" t="s">
-        <v>79</v>
+        <v>297</v>
       </c>
       <c r="BV9" t="s">
         <v>79</v>
@@ -3692,223 +3740,223 @@
     </row>
     <row r="10" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B10" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C10" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="D10" t="s">
-        <v>215</v>
+        <v>300</v>
       </c>
       <c r="E10" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F10" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="G10" t="s">
         <v>79</v>
       </c>
       <c r="H10" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="I10" t="s">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="J10" t="s">
-        <v>292</v>
+        <v>79</v>
       </c>
       <c r="K10" t="s">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="L10" t="s">
+        <v>79</v>
+      </c>
+      <c r="M10" t="s">
+        <v>79</v>
+      </c>
+      <c r="N10" t="s">
+        <v>79</v>
+      </c>
+      <c r="O10" t="s">
+        <v>79</v>
+      </c>
+      <c r="P10" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>79</v>
+      </c>
+      <c r="R10" t="s">
+        <v>79</v>
+      </c>
+      <c r="S10" t="s">
+        <v>224</v>
+      </c>
+      <c r="T10" t="s">
+        <v>225</v>
+      </c>
+      <c r="U10" t="s">
+        <v>79</v>
+      </c>
+      <c r="V10" t="s">
+        <v>79</v>
+      </c>
+      <c r="W10" t="s">
+        <v>79</v>
+      </c>
+      <c r="X10" t="s">
+        <v>226</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>302</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>301</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>229</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>143</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>230</v>
+      </c>
+      <c r="AE10" t="s">
         <v>89</v>
       </c>
-      <c r="M10" t="s">
-        <v>293</v>
-      </c>
-      <c r="N10" t="s">
-        <v>294</v>
-      </c>
-      <c r="O10" t="s">
-        <v>295</v>
-      </c>
-      <c r="P10" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>219</v>
-      </c>
-      <c r="R10" t="s">
-        <v>88</v>
-      </c>
-      <c r="S10" t="s">
-        <v>79</v>
-      </c>
-      <c r="T10" t="s">
-        <v>79</v>
-      </c>
-      <c r="U10" t="s">
-        <v>79</v>
-      </c>
-      <c r="V10" t="s">
-        <v>79</v>
-      </c>
-      <c r="W10" t="s">
-        <v>79</v>
-      </c>
-      <c r="X10" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>79</v>
-      </c>
       <c r="AF10" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="AG10" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AH10" t="s">
+        <v>231</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>232</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>303</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>234</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AY10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>79</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>79</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>235</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>236</v>
+      </c>
+      <c r="BE10" t="s">
+        <v>143</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>237</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>238</v>
+      </c>
+      <c r="BI10" t="s">
+        <v>239</v>
+      </c>
+      <c r="BJ10" t="s">
+        <v>143</v>
+      </c>
+      <c r="BK10" t="s">
+        <v>240</v>
+      </c>
+      <c r="BL10" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>241</v>
+      </c>
+      <c r="BN10" t="s">
         <v>242</v>
       </c>
-      <c r="AI10" t="s">
+      <c r="BO10" t="s">
+        <v>143</v>
+      </c>
+      <c r="BP10" t="s">
         <v>243</v>
       </c>
-      <c r="AJ10" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>101</v>
-      </c>
-      <c r="AL10" t="s">
+      <c r="BQ10" t="s">
+        <v>79</v>
+      </c>
+      <c r="BR10" t="s">
         <v>244</v>
       </c>
-      <c r="AM10" t="s">
-        <v>296</v>
-      </c>
-      <c r="AN10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AO10" t="s">
-        <v>100</v>
-      </c>
-      <c r="AP10" t="s">
-        <v>101</v>
-      </c>
-      <c r="AQ10" t="s">
-        <v>102</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>228</v>
-      </c>
-      <c r="AS10" t="s">
-        <v>297</v>
-      </c>
-      <c r="AT10" t="s">
-        <v>298</v>
-      </c>
-      <c r="AU10" t="s">
-        <v>284</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>299</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>228</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>300</v>
-      </c>
-      <c r="AY10" t="s">
-        <v>301</v>
-      </c>
-      <c r="AZ10" t="s">
-        <v>240</v>
-      </c>
-      <c r="BA10" t="s">
-        <v>302</v>
-      </c>
-      <c r="BB10" t="s">
-        <v>303</v>
-      </c>
-      <c r="BC10" t="s">
-        <v>304</v>
-      </c>
-      <c r="BD10" t="s">
-        <v>305</v>
-      </c>
-      <c r="BE10" t="s">
-        <v>240</v>
-      </c>
-      <c r="BF10" t="s">
-        <v>306</v>
-      </c>
-      <c r="BG10" t="s">
-        <v>79</v>
-      </c>
-      <c r="BH10" t="s">
-        <v>307</v>
-      </c>
-      <c r="BI10" t="s">
-        <v>308</v>
-      </c>
-      <c r="BJ10" t="s">
-        <v>309</v>
-      </c>
-      <c r="BK10" t="s">
-        <v>310</v>
-      </c>
-      <c r="BL10" t="s">
-        <v>79</v>
-      </c>
-      <c r="BM10" t="s">
-        <v>311</v>
-      </c>
-      <c r="BN10" t="s">
-        <v>312</v>
-      </c>
-      <c r="BO10" t="s">
-        <v>313</v>
-      </c>
-      <c r="BP10" t="s">
-        <v>314</v>
-      </c>
-      <c r="BQ10" t="s">
-        <v>79</v>
-      </c>
-      <c r="BR10" t="s">
-        <v>315</v>
-      </c>
       <c r="BS10" t="s">
-        <v>316</v>
+        <v>245</v>
       </c>
       <c r="BT10" t="s">
-        <v>317</v>
+        <v>143</v>
       </c>
       <c r="BU10" t="s">
-        <v>318</v>
+        <v>246</v>
       </c>
       <c r="BV10" t="s">
         <v>79</v>
@@ -3916,223 +3964,223 @@
     </row>
     <row r="11" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>212</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s">
+        <v>304</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" t="s">
+        <v>305</v>
+      </c>
+      <c r="E11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11" t="s">
+        <v>306</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" t="s">
+        <v>79</v>
+      </c>
+      <c r="J11" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" t="s">
+        <v>79</v>
+      </c>
+      <c r="M11" t="s">
+        <v>79</v>
+      </c>
+      <c r="N11" t="s">
+        <v>79</v>
+      </c>
+      <c r="O11" t="s">
+        <v>79</v>
+      </c>
+      <c r="P11" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>79</v>
+      </c>
+      <c r="R11" t="s">
+        <v>79</v>
+      </c>
+      <c r="S11" t="s">
+        <v>307</v>
+      </c>
+      <c r="T11" t="s">
+        <v>308</v>
+      </c>
+      <c r="U11" t="s">
+        <v>309</v>
+      </c>
+      <c r="V11" t="s">
+        <v>310</v>
+      </c>
+      <c r="W11" t="s">
+        <v>79</v>
+      </c>
+      <c r="X11" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>311</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>311</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>312</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>313</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>314</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>147</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>315</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>79</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>79</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>316</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>317</v>
+      </c>
+      <c r="BE11" t="s">
+        <v>318</v>
+      </c>
+      <c r="BF11" t="s">
         <v>319</v>
       </c>
-      <c r="C11" t="s">
-        <v>214</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="BG11" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH11" t="s">
         <v>320</v>
       </c>
-      <c r="E11" t="s">
-        <v>212</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="BI11" t="s">
         <v>321</v>
       </c>
-      <c r="G11" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" t="s">
-        <v>188</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="BJ11" t="s">
         <v>322</v>
       </c>
-      <c r="J11" t="s">
+      <c r="BK11" t="s">
         <v>323</v>
       </c>
-      <c r="K11" t="s">
+      <c r="BL11" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM11" t="s">
         <v>324</v>
       </c>
-      <c r="L11" t="s">
-        <v>89</v>
-      </c>
-      <c r="M11" t="s">
-        <v>220</v>
-      </c>
-      <c r="N11" t="s">
-        <v>221</v>
-      </c>
-      <c r="O11" t="s">
-        <v>222</v>
-      </c>
-      <c r="P11" t="s">
+      <c r="BN11" t="s">
         <v>325</v>
       </c>
-      <c r="Q11" t="s">
-        <v>324</v>
-      </c>
-      <c r="R11" t="s">
-        <v>88</v>
-      </c>
-      <c r="S11" t="s">
-        <v>79</v>
-      </c>
-      <c r="T11" t="s">
-        <v>79</v>
-      </c>
-      <c r="U11" t="s">
-        <v>79</v>
-      </c>
-      <c r="V11" t="s">
-        <v>79</v>
-      </c>
-      <c r="W11" t="s">
-        <v>79</v>
-      </c>
-      <c r="X11" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>324</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH11" t="s">
+      <c r="BO11" t="s">
+        <v>322</v>
+      </c>
+      <c r="BP11" t="s">
         <v>326</v>
       </c>
-      <c r="AI11" t="s">
+      <c r="BQ11" t="s">
+        <v>79</v>
+      </c>
+      <c r="BR11" t="s">
         <v>327</v>
       </c>
-      <c r="AJ11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK11" t="s">
+      <c r="BS11" t="s">
         <v>328</v>
       </c>
-      <c r="AL11" t="s">
+      <c r="BT11" t="s">
+        <v>322</v>
+      </c>
+      <c r="BU11" t="s">
         <v>329</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>228</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>330</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>331</v>
-      </c>
-      <c r="AP11" t="s">
-        <v>332</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>333</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>228</v>
-      </c>
-      <c r="AS11" t="s">
-        <v>334</v>
-      </c>
-      <c r="AT11" t="s">
-        <v>325</v>
-      </c>
-      <c r="AU11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>335</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>336</v>
-      </c>
-      <c r="AY11" t="s">
-        <v>337</v>
-      </c>
-      <c r="AZ11" t="s">
-        <v>338</v>
-      </c>
-      <c r="BA11" t="s">
-        <v>339</v>
-      </c>
-      <c r="BB11" t="s">
-        <v>79</v>
-      </c>
-      <c r="BC11" t="s">
-        <v>340</v>
-      </c>
-      <c r="BD11" t="s">
-        <v>341</v>
-      </c>
-      <c r="BE11" t="s">
-        <v>105</v>
-      </c>
-      <c r="BF11" t="s">
-        <v>342</v>
-      </c>
-      <c r="BG11" t="s">
-        <v>79</v>
-      </c>
-      <c r="BH11" t="s">
-        <v>343</v>
-      </c>
-      <c r="BI11" t="s">
-        <v>344</v>
-      </c>
-      <c r="BJ11" t="s">
-        <v>345</v>
-      </c>
-      <c r="BK11" t="s">
-        <v>346</v>
-      </c>
-      <c r="BL11" t="s">
-        <v>79</v>
-      </c>
-      <c r="BM11" t="s">
-        <v>347</v>
-      </c>
-      <c r="BN11" t="s">
-        <v>348</v>
-      </c>
-      <c r="BO11" t="s">
-        <v>349</v>
-      </c>
-      <c r="BP11" t="s">
-        <v>350</v>
-      </c>
-      <c r="BQ11" t="s">
-        <v>79</v>
-      </c>
-      <c r="BR11" t="s">
-        <v>79</v>
-      </c>
-      <c r="BS11" t="s">
-        <v>79</v>
-      </c>
-      <c r="BT11" t="s">
-        <v>79</v>
-      </c>
-      <c r="BU11" t="s">
-        <v>79</v>
       </c>
       <c r="BV11" t="s">
         <v>79</v>
@@ -4140,208 +4188,208 @@
     </row>
     <row r="12" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>212</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="C12" t="s">
         <v>76</v>
       </c>
       <c r="D12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" t="s">
+        <v>332</v>
+      </c>
+      <c r="G12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" t="s">
+        <v>333</v>
+      </c>
+      <c r="J12" t="s">
+        <v>334</v>
+      </c>
+      <c r="K12" t="s">
+        <v>335</v>
+      </c>
+      <c r="L12" t="s">
+        <v>84</v>
+      </c>
+      <c r="M12" t="s">
+        <v>85</v>
+      </c>
+      <c r="N12" t="s">
+        <v>86</v>
+      </c>
+      <c r="O12" t="s">
+        <v>87</v>
+      </c>
+      <c r="P12" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>335</v>
+      </c>
+      <c r="R12" t="s">
+        <v>89</v>
+      </c>
+      <c r="S12" t="s">
+        <v>79</v>
+      </c>
+      <c r="T12" t="s">
+        <v>79</v>
+      </c>
+      <c r="U12" t="s">
+        <v>79</v>
+      </c>
+      <c r="V12" t="s">
+        <v>79</v>
+      </c>
+      <c r="W12" t="s">
+        <v>79</v>
+      </c>
+      <c r="X12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>335</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>336</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>337</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>290</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>338</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>339</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>340</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>341</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>342</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>149</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>150</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>152</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>343</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>344</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>318</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>345</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>346</v>
+      </c>
+      <c r="BD12" t="s">
+        <v>347</v>
+      </c>
+      <c r="BE12" t="s">
+        <v>341</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>348</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>349</v>
+      </c>
+      <c r="BI12" t="s">
+        <v>350</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>351</v>
+      </c>
+      <c r="BK12" t="s">
         <v>352</v>
       </c>
-      <c r="E12" t="s">
-        <v>212</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="BL12" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM12" t="s">
         <v>353</v>
       </c>
-      <c r="G12" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12" t="s">
-        <v>115</v>
-      </c>
-      <c r="I12" t="s">
-        <v>353</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="BN12" t="s">
         <v>354</v>
       </c>
-      <c r="K12" t="s">
+      <c r="BO12" t="s">
+        <v>351</v>
+      </c>
+      <c r="BP12" t="s">
         <v>355</v>
-      </c>
-      <c r="L12" t="s">
-        <v>89</v>
-      </c>
-      <c r="M12" t="s">
-        <v>356</v>
-      </c>
-      <c r="N12" t="s">
-        <v>357</v>
-      </c>
-      <c r="O12" t="s">
-        <v>295</v>
-      </c>
-      <c r="P12" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>355</v>
-      </c>
-      <c r="R12" t="s">
-        <v>88</v>
-      </c>
-      <c r="S12" t="s">
-        <v>79</v>
-      </c>
-      <c r="T12" t="s">
-        <v>79</v>
-      </c>
-      <c r="U12" t="s">
-        <v>79</v>
-      </c>
-      <c r="V12" t="s">
-        <v>79</v>
-      </c>
-      <c r="W12" t="s">
-        <v>79</v>
-      </c>
-      <c r="X12" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM12" t="s">
-        <v>228</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AQ12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR12" t="s">
-        <v>303</v>
-      </c>
-      <c r="AS12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AT12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AU12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AV12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AW12" t="s">
-        <v>358</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AY12" t="s">
-        <v>79</v>
-      </c>
-      <c r="AZ12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BA12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BB12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BC12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BD12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BF12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BG12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BH12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BI12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BJ12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BK12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BL12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BM12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BO12" t="s">
-        <v>79</v>
-      </c>
-      <c r="BP12" t="s">
-        <v>79</v>
       </c>
       <c r="BQ12" t="s">
         <v>79</v>
@@ -4364,223 +4412,223 @@
     </row>
     <row r="13" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B13" t="s">
+        <v>356</v>
+      </c>
+      <c r="C13" t="s">
+        <v>357</v>
+      </c>
+      <c r="D13" t="s">
+        <v>358</v>
+      </c>
+      <c r="E13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F13" t="s">
         <v>359</v>
       </c>
-      <c r="C13" t="s">
+      <c r="G13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" t="s">
+        <v>157</v>
+      </c>
+      <c r="I13" t="s">
+        <v>79</v>
+      </c>
+      <c r="J13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K13" t="s">
+        <v>79</v>
+      </c>
+      <c r="L13" t="s">
+        <v>79</v>
+      </c>
+      <c r="M13" t="s">
+        <v>79</v>
+      </c>
+      <c r="N13" t="s">
+        <v>79</v>
+      </c>
+      <c r="O13" t="s">
+        <v>79</v>
+      </c>
+      <c r="P13" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>79</v>
+      </c>
+      <c r="R13" t="s">
+        <v>79</v>
+      </c>
+      <c r="S13" t="s">
         <v>360</v>
       </c>
-      <c r="D13" t="s">
-        <v>264</v>
-      </c>
-      <c r="E13" t="s">
-        <v>212</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="T13" t="s">
         <v>361</v>
       </c>
-      <c r="G13" t="s">
-        <v>79</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="U13" t="s">
+        <v>79</v>
+      </c>
+      <c r="V13" t="s">
+        <v>79</v>
+      </c>
+      <c r="W13" t="s">
+        <v>79</v>
+      </c>
+      <c r="X13" t="s">
         <v>362</v>
       </c>
-      <c r="I13" t="s">
+      <c r="Y13" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>227</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>228</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>229</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>143</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>230</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>89</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>230</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>235</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>236</v>
+      </c>
+      <c r="AJ13" t="s">
         <v>363</v>
       </c>
-      <c r="J13" t="s">
+      <c r="AK13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>237</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>238</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>239</v>
+      </c>
+      <c r="BE13" t="s">
+        <v>143</v>
+      </c>
+      <c r="BF13" t="s">
+        <v>240</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH13" t="s">
+        <v>241</v>
+      </c>
+      <c r="BI13" t="s">
+        <v>242</v>
+      </c>
+      <c r="BJ13" t="s">
+        <v>143</v>
+      </c>
+      <c r="BK13" t="s">
+        <v>243</v>
+      </c>
+      <c r="BL13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM13" t="s">
+        <v>244</v>
+      </c>
+      <c r="BN13" t="s">
+        <v>245</v>
+      </c>
+      <c r="BO13" t="s">
+        <v>143</v>
+      </c>
+      <c r="BP13" t="s">
+        <v>246</v>
+      </c>
+      <c r="BQ13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BR13" t="s">
         <v>364</v>
       </c>
-      <c r="K13" t="s">
-        <v>268</v>
-      </c>
-      <c r="L13" t="s">
-        <v>89</v>
-      </c>
-      <c r="M13" t="s">
+      <c r="BS13" t="s">
         <v>365</v>
       </c>
-      <c r="N13" t="s">
+      <c r="BT13" t="s">
+        <v>143</v>
+      </c>
+      <c r="BU13" t="s">
         <v>366</v>
-      </c>
-      <c r="O13" t="s">
-        <v>222</v>
-      </c>
-      <c r="P13" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>268</v>
-      </c>
-      <c r="R13" t="s">
-        <v>88</v>
-      </c>
-      <c r="S13" t="s">
-        <v>79</v>
-      </c>
-      <c r="T13" t="s">
-        <v>79</v>
-      </c>
-      <c r="U13" t="s">
-        <v>79</v>
-      </c>
-      <c r="V13" t="s">
-        <v>79</v>
-      </c>
-      <c r="W13" t="s">
-        <v>79</v>
-      </c>
-      <c r="X13" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>268</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>228</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AP13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AQ13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>228</v>
-      </c>
-      <c r="AS13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AU13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AV13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AW13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AY13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AZ13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BA13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BB13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BC13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BD13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BF13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BG13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BH13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BI13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BJ13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BK13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BL13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BM13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BO13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BP13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BQ13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BR13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BS13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BT13" t="s">
-        <v>79</v>
-      </c>
-      <c r="BU13" t="s">
-        <v>79</v>
       </c>
       <c r="BV13" t="s">
         <v>79</v>
@@ -4588,64 +4636,64 @@
     </row>
     <row r="14" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" t="s">
         <v>367</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>368</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>184</v>
+      </c>
+      <c r="E14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" t="s">
         <v>369</v>
       </c>
-      <c r="D14" t="s">
+      <c r="G14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" t="s">
+        <v>124</v>
+      </c>
+      <c r="I14" t="s">
+        <v>186</v>
+      </c>
+      <c r="J14" t="s">
         <v>370</v>
       </c>
-      <c r="E14" t="s">
-        <v>367</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="K14" t="s">
+        <v>83</v>
+      </c>
+      <c r="L14" t="s">
+        <v>84</v>
+      </c>
+      <c r="M14" t="s">
         <v>371</v>
       </c>
-      <c r="G14" t="s">
-        <v>79</v>
-      </c>
-      <c r="H14" t="s">
-        <v>115</v>
-      </c>
-      <c r="I14" t="s">
-        <v>79</v>
-      </c>
-      <c r="J14" t="s">
-        <v>79</v>
-      </c>
-      <c r="K14" t="s">
-        <v>79</v>
-      </c>
-      <c r="L14" t="s">
-        <v>79</v>
-      </c>
-      <c r="M14" t="s">
-        <v>79</v>
-      </c>
       <c r="N14" t="s">
-        <v>79</v>
+        <v>372</v>
       </c>
       <c r="O14" t="s">
-        <v>79</v>
+        <v>373</v>
       </c>
       <c r="P14" t="s">
         <v>79</v>
       </c>
       <c r="Q14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="R14" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="S14" t="s">
-        <v>372</v>
+        <v>79</v>
       </c>
       <c r="T14" t="s">
-        <v>373</v>
+        <v>79</v>
       </c>
       <c r="U14" t="s">
         <v>79</v>
@@ -4657,121 +4705,121 @@
         <v>79</v>
       </c>
       <c r="X14" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>205</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>206</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>143</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM14" t="s">
         <v>374</v>
       </c>
-      <c r="Y14" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z14" t="s">
+      <c r="AN14" t="s">
+        <v>141</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>142</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>143</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>144</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>103</v>
+      </c>
+      <c r="AS14" t="s">
         <v>375</v>
       </c>
-      <c r="AA14" t="s">
+      <c r="AT14" t="s">
         <v>376</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="AU14" t="s">
+        <v>351</v>
+      </c>
+      <c r="AV14" t="s">
         <v>377</v>
       </c>
-      <c r="AC14" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD14" t="s">
+      <c r="AW14" t="s">
+        <v>103</v>
+      </c>
+      <c r="AX14" t="s">
         <v>378</v>
       </c>
-      <c r="AE14" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>378</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH14" t="s">
+      <c r="AY14" t="s">
         <v>379</v>
       </c>
-      <c r="AI14" t="s">
+      <c r="AZ14" t="s">
+        <v>203</v>
+      </c>
+      <c r="BA14" t="s">
         <v>380</v>
       </c>
-      <c r="AJ14" t="s">
+      <c r="BB14" t="s">
         <v>381</v>
       </c>
-      <c r="AK14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL14" t="s">
+      <c r="BC14" t="s">
         <v>382</v>
       </c>
-      <c r="AM14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AP14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AQ14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AS14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AT14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AU14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AV14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AW14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AY14" t="s">
-        <v>79</v>
-      </c>
-      <c r="AZ14" t="s">
-        <v>79</v>
-      </c>
-      <c r="BA14" t="s">
-        <v>79</v>
-      </c>
-      <c r="BB14" t="s">
-        <v>79</v>
-      </c>
-      <c r="BC14" t="s">
+      <c r="BD14" t="s">
         <v>383</v>
       </c>
-      <c r="BD14" t="s">
+      <c r="BE14" t="s">
+        <v>203</v>
+      </c>
+      <c r="BF14" t="s">
         <v>384</v>
       </c>
-      <c r="BE14" t="s">
-        <v>101</v>
-      </c>
-      <c r="BF14" t="s">
+      <c r="BG14" t="s">
+        <v>79</v>
+      </c>
+      <c r="BH14" t="s">
         <v>385</v>
       </c>
-      <c r="BG14" t="s">
-        <v>79</v>
-      </c>
-      <c r="BH14" t="s">
+      <c r="BI14" t="s">
         <v>386</v>
       </c>
-      <c r="BI14" t="s">
+      <c r="BJ14" t="s">
         <v>387</v>
-      </c>
-      <c r="BJ14" t="s">
-        <v>101</v>
       </c>
       <c r="BK14" t="s">
         <v>388</v>
@@ -4786,25 +4834,25 @@
         <v>390</v>
       </c>
       <c r="BO14" t="s">
-        <v>101</v>
+        <v>391</v>
       </c>
       <c r="BP14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="BQ14" t="s">
         <v>79</v>
       </c>
       <c r="BR14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="BS14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="BT14" t="s">
-        <v>101</v>
+        <v>395</v>
       </c>
       <c r="BU14" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="BV14" t="s">
         <v>79</v>
@@ -4812,64 +4860,64 @@
     </row>
     <row r="15" spans="1:74" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>367</v>
+        <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C15" t="s">
-        <v>396</v>
+        <v>183</v>
       </c>
       <c r="D15" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E15" t="s">
-        <v>367</v>
+        <v>74</v>
       </c>
       <c r="F15" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G15" t="s">
         <v>79</v>
       </c>
       <c r="H15" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s">
-        <v>79</v>
+        <v>400</v>
       </c>
       <c r="J15" t="s">
-        <v>79</v>
+        <v>401</v>
       </c>
       <c r="K15" t="s">
-        <v>79</v>
+        <v>402</v>
       </c>
       <c r="L15" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M15" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="N15" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="O15" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="P15" t="s">
-        <v>79</v>
+        <v>403</v>
       </c>
       <c r="Q15" t="s">
-        <v>79</v>
+        <v>402</v>
       </c>
       <c r="R15" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="S15" t="s">
-        <v>372</v>
+        <v>79</v>
       </c>
       <c r="T15" t="s">
-        <v>373</v>
+        <v>79</v>
       </c>
       <c r="U15" t="s">
         <v>79</v>
@@ -4881,13 +4929,13 @@
         <v>79</v>
       </c>
       <c r="X15" t="s">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="Y15" t="s">
         <v>79</v>
       </c>
       <c r="Z15" t="s">
-        <v>399</v>
+        <v>79</v>
       </c>
       <c r="AA15" t="s">
         <v>79</v>
@@ -4899,362 +4947,138 @@
         <v>79</v>
       </c>
       <c r="AD15" t="s">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="AE15" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AF15" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="AG15" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AH15" t="s">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="AI15" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="AJ15" t="s">
-        <v>400</v>
+        <v>79</v>
       </c>
       <c r="AK15" t="s">
-        <v>79</v>
+        <v>406</v>
       </c>
       <c r="AL15" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="AM15" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AN15" t="s">
-        <v>79</v>
+        <v>408</v>
       </c>
       <c r="AO15" t="s">
-        <v>79</v>
+        <v>409</v>
       </c>
       <c r="AP15" t="s">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="AQ15" t="s">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AR15" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AS15" t="s">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="AT15" t="s">
-        <v>79</v>
+        <v>403</v>
       </c>
       <c r="AU15" t="s">
         <v>79</v>
       </c>
       <c r="AV15" t="s">
-        <v>79</v>
+        <v>413</v>
       </c>
       <c r="AW15" t="s">
         <v>79</v>
       </c>
       <c r="AX15" t="s">
-        <v>79</v>
+        <v>414</v>
       </c>
       <c r="AY15" t="s">
-        <v>79</v>
+        <v>415</v>
       </c>
       <c r="AZ15" t="s">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="BA15" t="s">
-        <v>79</v>
+        <v>417</v>
       </c>
       <c r="BB15" t="s">
         <v>79</v>
       </c>
       <c r="BC15" t="s">
-        <v>383</v>
+        <v>418</v>
       </c>
       <c r="BD15" t="s">
-        <v>384</v>
+        <v>419</v>
       </c>
       <c r="BE15" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="BF15" t="s">
-        <v>385</v>
+        <v>420</v>
       </c>
       <c r="BG15" t="s">
         <v>79</v>
       </c>
       <c r="BH15" t="s">
-        <v>386</v>
+        <v>421</v>
       </c>
       <c r="BI15" t="s">
-        <v>387</v>
+        <v>422</v>
       </c>
       <c r="BJ15" t="s">
-        <v>101</v>
+        <v>423</v>
       </c>
       <c r="BK15" t="s">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="BL15" t="s">
         <v>79</v>
       </c>
       <c r="BM15" t="s">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="BN15" t="s">
-        <v>390</v>
+        <v>426</v>
       </c>
       <c r="BO15" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="BP15" t="s">
-        <v>391</v>
+        <v>427</v>
       </c>
       <c r="BQ15" t="s">
         <v>79</v>
       </c>
       <c r="BR15" t="s">
-        <v>392</v>
+        <v>79</v>
       </c>
       <c r="BS15" t="s">
-        <v>393</v>
+        <v>79</v>
       </c>
       <c r="BT15" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="BU15" t="s">
-        <v>394</v>
+        <v>79</v>
       </c>
       <c r="BV15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:74" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>367</v>
-      </c>
-      <c r="B16" t="s">
-        <v>401</v>
-      </c>
-      <c r="C16" t="s">
-        <v>402</v>
-      </c>
-      <c r="D16" t="s">
-        <v>403</v>
-      </c>
-      <c r="E16" t="s">
-        <v>367</v>
-      </c>
-      <c r="F16" t="s">
-        <v>404</v>
-      </c>
-      <c r="G16" t="s">
-        <v>79</v>
-      </c>
-      <c r="H16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I16" t="s">
-        <v>79</v>
-      </c>
-      <c r="J16" t="s">
-        <v>79</v>
-      </c>
-      <c r="K16" t="s">
-        <v>79</v>
-      </c>
-      <c r="L16" t="s">
-        <v>79</v>
-      </c>
-      <c r="M16" t="s">
-        <v>79</v>
-      </c>
-      <c r="N16" t="s">
-        <v>79</v>
-      </c>
-      <c r="O16" t="s">
-        <v>79</v>
-      </c>
-      <c r="P16" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>79</v>
-      </c>
-      <c r="R16" t="s">
-        <v>79</v>
-      </c>
-      <c r="S16" t="s">
-        <v>405</v>
-      </c>
-      <c r="T16" t="s">
-        <v>406</v>
-      </c>
-      <c r="U16" t="s">
-        <v>79</v>
-      </c>
-      <c r="V16" t="s">
-        <v>79</v>
-      </c>
-      <c r="W16" t="s">
-        <v>79</v>
-      </c>
-      <c r="X16" t="s">
-        <v>407</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>375</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>376</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>377</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>378</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>378</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>89</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>383</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>384</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>408</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL16" t="s">
-        <v>385</v>
-      </c>
-      <c r="AM16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AP16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AQ16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AS16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AT16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AU16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AV16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AW16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AX16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AY16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AZ16" t="s">
-        <v>79</v>
-      </c>
-      <c r="BA16" t="s">
-        <v>79</v>
-      </c>
-      <c r="BB16" t="s">
-        <v>79</v>
-      </c>
-      <c r="BC16" t="s">
-        <v>386</v>
-      </c>
-      <c r="BD16" t="s">
-        <v>387</v>
-      </c>
-      <c r="BE16" t="s">
-        <v>101</v>
-      </c>
-      <c r="BF16" t="s">
-        <v>388</v>
-      </c>
-      <c r="BG16" t="s">
-        <v>79</v>
-      </c>
-      <c r="BH16" t="s">
-        <v>389</v>
-      </c>
-      <c r="BI16" t="s">
-        <v>390</v>
-      </c>
-      <c r="BJ16" t="s">
-        <v>101</v>
-      </c>
-      <c r="BK16" t="s">
-        <v>391</v>
-      </c>
-      <c r="BL16" t="s">
-        <v>79</v>
-      </c>
-      <c r="BM16" t="s">
-        <v>392</v>
-      </c>
-      <c r="BN16" t="s">
-        <v>393</v>
-      </c>
-      <c r="BO16" t="s">
-        <v>101</v>
-      </c>
-      <c r="BP16" t="s">
-        <v>394</v>
-      </c>
-      <c r="BQ16" t="s">
-        <v>79</v>
-      </c>
-      <c r="BR16" t="s">
-        <v>409</v>
-      </c>
-      <c r="BS16" t="s">
-        <v>410</v>
-      </c>
-      <c r="BT16" t="s">
-        <v>101</v>
-      </c>
-      <c r="BU16" t="s">
-        <v>411</v>
-      </c>
-      <c r="BV16" t="s">
         <v>79</v>
       </c>
     </row>
